--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="536">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -805,6 +805,9 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>387713003</t>
+  </si>
+  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -814,7 +817,7 @@
     <t>C*E.1</t>
   </si>
   <si>
-    <t>1313: fixed value = 387713003</t>
+    <t>1313: fixed value = #387713003</t>
   </si>
   <si>
     <t>Procedure.category.coding.display</t>
@@ -1572,7 +1575,7 @@
     <t>Procedure.complication.coding.code</t>
   </si>
   <si>
-    <t>1297: fixed value = 22298006 when SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>
+    <t>1297: fixed value = #22298006 when SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>
   </si>
   <si>
     <t>Procedure.complication.coding.display</t>
@@ -5149,7 +5152,7 @@
         <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>79</v>
@@ -5188,7 +5191,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5206,16 +5209,16 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -5223,10 +5226,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5252,14 +5255,14 @@
         <v>212</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5308,7 +5311,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5326,13 +5329,13 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5343,10 +5346,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5369,19 +5372,19 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5430,7 +5433,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5448,13 +5451,13 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5465,10 +5468,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5494,16 +5497,16 @@
         <v>212</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5552,7 +5555,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5570,13 +5573,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5587,14 +5590,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5616,14 +5619,14 @@
         <v>195</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5648,13 +5651,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5672,7 +5675,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5687,16 +5690,16 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5707,10 +5710,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5825,10 +5828,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5945,10 +5948,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6059,7 +6062,7 @@
         <v>231</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -6067,10 +6070,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6096,16 +6099,16 @@
         <v>212</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -6154,7 +6157,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6172,31 +6175,31 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6215,13 +6218,13 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6272,7 +6275,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>89</v>
@@ -6287,30 +6290,30 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6333,16 +6336,16 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6392,7 +6395,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6407,19 +6410,19 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -6427,10 +6430,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6453,16 +6456,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6500,7 +6503,7 @@
         <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
@@ -6510,7 +6513,7 @@
         <v>221</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6525,16 +6528,16 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6545,13 +6548,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>79</v>
@@ -6573,16 +6576,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6632,7 +6635,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6647,33 +6650,33 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -6695,16 +6698,16 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6754,7 +6757,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6769,16 +6772,16 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6789,10 +6792,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6907,10 +6910,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7027,10 +7030,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7053,16 +7056,16 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7112,7 +7115,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7121,7 +7124,7 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>101</v>
@@ -7130,27 +7133,27 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7173,23 +7176,23 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="R43" t="s" s="2">
         <v>79</v>
@@ -7234,7 +7237,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7243,7 +7246,7 @@
         <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>101</v>
@@ -7252,27 +7255,27 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7295,13 +7298,13 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7352,7 +7355,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7370,10 +7373,10 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7387,10 +7390,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7413,13 +7416,13 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7470,7 +7473,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7488,10 +7491,10 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>79</v>
@@ -7505,10 +7508,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7531,13 +7534,13 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7588,7 +7591,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7603,10 +7606,10 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7623,10 +7626,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7741,10 +7744,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7861,14 +7864,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7890,10 +7893,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>138</v>
@@ -7948,7 +7951,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7983,10 +7986,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8012,14 +8015,14 @@
         <v>195</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -8047,10 +8050,10 @@
         <v>199</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -8068,7 +8071,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8083,16 +8086,16 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -8103,10 +8106,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8129,17 +8132,17 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8188,7 +8191,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>89</v>
@@ -8203,30 +8206,30 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8249,17 +8252,17 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8308,7 +8311,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8326,7 +8329,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -8343,10 +8346,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8369,17 +8372,17 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8428,7 +8431,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8446,27 +8449,27 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8492,13 +8495,13 @@
         <v>195</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8527,10 +8530,10 @@
         <v>199</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8548,7 +8551,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8563,13 +8566,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8583,10 +8586,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8701,10 +8704,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8821,10 +8824,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8943,10 +8946,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8972,16 +8975,16 @@
         <v>212</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9030,7 +9033,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9048,27 +9051,27 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9091,16 +9094,16 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9150,7 +9153,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9165,13 +9168,13 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>79</v>
@@ -9185,10 +9188,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9214,13 +9217,13 @@
         <v>195</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9249,10 +9252,10 @@
         <v>199</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -9270,7 +9273,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9288,13 +9291,13 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9305,10 +9308,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9334,13 +9337,13 @@
         <v>195</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9369,10 +9372,10 @@
         <v>199</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>79</v>
@@ -9390,7 +9393,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9408,7 +9411,7 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
@@ -9425,10 +9428,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9451,16 +9454,16 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9510,7 +9513,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9528,7 +9531,7 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -9545,10 +9548,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9574,13 +9577,13 @@
         <v>195</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9609,10 +9612,10 @@
         <v>199</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
@@ -9630,7 +9633,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9648,7 +9651,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9665,10 +9668,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9783,10 +9786,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9903,10 +9906,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10025,10 +10028,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10143,10 +10146,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10263,10 +10266,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10385,10 +10388,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10505,10 +10508,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10590,7 +10593,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10608,16 +10611,16 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>79</v>
@@ -10625,10 +10628,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10654,14 +10657,14 @@
         <v>212</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10710,7 +10713,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10728,13 +10731,13 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10745,10 +10748,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10771,19 +10774,19 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10832,7 +10835,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10850,13 +10853,13 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10867,10 +10870,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10896,16 +10899,16 @@
         <v>212</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10954,7 +10957,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10972,13 +10975,13 @@
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -10989,10 +10992,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11015,17 +11018,17 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11074,7 +11077,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11092,7 +11095,7 @@
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>79</v>
@@ -11109,10 +11112,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11138,10 +11141,10 @@
         <v>195</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11171,10 +11174,10 @@
         <v>199</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>79</v>
@@ -11192,7 +11195,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11210,7 +11213,7 @@
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>79</v>
@@ -11227,10 +11230,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11253,13 +11256,13 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11310,7 +11313,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11325,19 +11328,19 @@
         <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>79</v>
@@ -11345,10 +11348,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11371,13 +11374,13 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11428,7 +11431,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11446,7 +11449,7 @@
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>79</v>
@@ -11463,10 +11466,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11581,10 +11584,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11701,14 +11704,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11730,10 +11733,10 @@
         <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>138</v>
@@ -11788,7 +11791,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11823,10 +11826,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11852,10 +11855,10 @@
         <v>195</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11885,10 +11888,10 @@
         <v>113</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>79</v>
@@ -11906,7 +11909,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11924,7 +11927,7 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>79</v>
@@ -11941,10 +11944,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11967,13 +11970,13 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12024,7 +12027,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>89</v>
@@ -12042,7 +12045,7 @@
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>79</v>
@@ -12059,10 +12062,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12085,19 +12088,19 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12146,7 +12149,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12164,7 +12167,7 @@
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>79</v>
@@ -12181,10 +12184,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12210,13 +12213,13 @@
         <v>195</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12245,10 +12248,10 @@
         <v>199</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>79</v>
@@ -12266,7 +12269,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12284,7 +12287,7 @@
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2733" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -733,6 +733,13 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;code value="387713003"/&gt;
+  &lt;display value="Surgical procedure"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -742,131 +749,7 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>Procedure.category.coding.id</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>387713003</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>1313: fixed value = #387713003</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
+    <t>1313: fixed value = http://snomed.info/sct#387713003 Surgical procedure</t>
   </si>
   <si>
     <t>Procedure.category.text</t>
@@ -1560,28 +1443,7 @@
     <t>Procedure.complication.coding</t>
   </si>
   <si>
-    <t>Procedure.complication.coding.id</t>
-  </si>
-  <si>
-    <t>Procedure.complication.coding.extension</t>
-  </si>
-  <si>
-    <t>Procedure.complication.coding.system</t>
-  </si>
-  <si>
-    <t>Procedure.complication.coding.version</t>
-  </si>
-  <si>
-    <t>Procedure.complication.coding.code</t>
-  </si>
-  <si>
-    <t>1297: fixed value = #22298006 when SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>
-  </si>
-  <si>
-    <t>Procedure.complication.coding.display</t>
-  </si>
-  <si>
-    <t>Procedure.complication.coding.userSelected</t>
+    <t>1297: fixed value = http://snomed.info/sct#22298006 Myocardial infarction (disorder) when SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>
   </si>
   <si>
     <t>Procedure.complication.text</t>
@@ -2056,11 +1918,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP85"/>
+  <dimension ref="A1:AP71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.70703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.93359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.61328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -2098,7 +1960,7 @@
     <col min="38" max="38" width="142.56640625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="115.109375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="143.515625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="56.90234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -4521,7 +4383,7 @@
         <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>79</v>
@@ -4552,7 +4414,7 @@
         <v>79</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>79</v>
+        <v>229</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>79</v>
@@ -4591,7 +4453,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4609,16 +4471,16 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
@@ -4626,10 +4488,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4649,19 +4511,23 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>212</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4709,7 +4575,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4721,19 +4587,19 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4744,44 +4610,44 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>134</v>
+        <v>243</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>136</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4805,55 +4671,55 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>79</v>
+        <v>252</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4864,10 +4730,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4887,23 +4753,19 @@
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4951,7 +4813,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4963,19 +4825,19 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>241</v>
+        <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4986,21 +4848,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>79</v>
@@ -5009,19 +4871,19 @@
         <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>136</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5059,43 +4921,43 @@
         <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -5106,10 +4968,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5120,7 +4982,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>90</v>
@@ -5132,17 +4994,19 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>109</v>
+        <v>224</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5152,7 +5016,7 @@
         <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>79</v>
@@ -5191,13 +5055,13 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
@@ -5209,13 +5073,13 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>257</v>
@@ -5243,7 +5107,7 @@
         <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>79</v>
@@ -5255,14 +5119,16 @@
         <v>212</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="O27" t="s" s="2">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5311,7 +5177,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5329,41 +5195,41 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>79</v>
+        <v>259</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>79</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>79</v>
@@ -5372,20 +5238,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5433,10 +5295,10 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>89</v>
@@ -5448,30 +5310,30 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>79</v>
+        <v>268</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>79</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5485,7 +5347,7 @@
         <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>79</v>
@@ -5494,20 +5356,18 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>278</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5555,7 +5415,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5570,19 +5430,19 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AM29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5597,11 +5457,11 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>89</v>
@@ -5616,7 +5476,7 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>195</v>
+        <v>283</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>284</v>
@@ -5624,10 +5484,10 @@
       <c r="M30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>286</v>
       </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5651,28 +5511,26 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB30" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Y30" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>79</v>
-      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>282</v>
@@ -5684,22 +5542,22 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5710,12 +5568,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
       </c>
@@ -5727,24 +5587,26 @@
         <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>212</v>
+        <v>294</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>213</v>
+        <v>284</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5793,7 +5655,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>215</v>
+        <v>282</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5802,68 +5664,70 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>216</v>
+        <v>289</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>79</v>
+        <v>291</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>79</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="D32" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>299</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>136</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>138</v>
+        <v>286</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5901,43 +5765,43 @@
         <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>222</v>
+        <v>282</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>216</v>
+        <v>289</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>79</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5948,10 +5812,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5962,32 +5826,28 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
@@ -6035,34 +5895,34 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>297</v>
+        <v>79</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -6070,46 +5930,44 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>275</v>
+        <v>136</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>276</v>
+        <v>218</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -6145,65 +6003,65 @@
         <v>79</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>302</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
@@ -6218,15 +6076,17 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6275,45 +6135,45 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>308</v>
+        <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6336,22 +6196,24 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q36" s="2"/>
+      <c r="Q36" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="R36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6395,7 +6257,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6404,36 +6266,36 @@
         <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>79</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6447,7 +6309,7 @@
         <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>79</v>
@@ -6456,17 +6318,15 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6503,17 +6363,19 @@
         <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AC37" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6522,22 +6384,22 @@
         <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6551,11 +6413,9 @@
         <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6567,7 +6427,7 @@
         <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>79</v>
@@ -6576,17 +6436,15 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>326</v>
-      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6635,7 +6493,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6644,28 +6502,28 @@
         <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>335</v>
+        <v>79</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -6673,11 +6531,9 @@
         <v>337</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>79</v>
       </c>
@@ -6686,10 +6542,10 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>79</v>
@@ -6698,17 +6554,15 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L39" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="M39" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6757,31 +6611,31 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>330</v>
+        <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6792,10 +6646,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6910,10 +6764,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6983,16 +6837,16 @@
         <v>79</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>222</v>
@@ -7030,44 +6884,46 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>334</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -7121,39 +6977,39 @@
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>351</v>
+        <v>132</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>353</v>
+        <v>79</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>354</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7167,7 +7023,7 @@
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>79</v>
@@ -7176,24 +7032,22 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>334</v>
+        <v>195</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q43" t="s" s="2">
-        <v>360</v>
-      </c>
+      <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
         <v>79</v>
       </c>
@@ -7213,13 +7067,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -7237,7 +7091,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7246,36 +7100,36 @@
         <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7283,13 +7137,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>79</v>
@@ -7298,16 +7152,18 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7355,10 +7211,10 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -7370,30 +7226,30 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>79</v>
+        <v>367</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7413,19 +7269,21 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
       </c>
@@ -7473,7 +7331,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7494,7 +7352,7 @@
         <v>375</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>79</v>
@@ -7508,10 +7366,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7522,10 +7380,10 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>79</v>
@@ -7534,16 +7392,18 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7591,13 +7451,13 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
@@ -7606,30 +7466,30 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AN46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7640,7 +7500,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7649,18 +7509,20 @@
         <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>213</v>
+        <v>386</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7685,13 +7547,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7709,28 +7571,28 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>215</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>216</v>
+        <v>392</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>79</v>
@@ -7744,21 +7606,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>79</v>
@@ -7770,17 +7632,15 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>135</v>
+        <v>212</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>136</v>
+        <v>213</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7829,19 +7689,19 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
@@ -7864,14 +7724,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>386</v>
+        <v>134</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7884,26 +7744,24 @@
         <v>79</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>387</v>
+        <v>136</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>388</v>
+        <v>218</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O49" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
       </c>
@@ -7939,19 +7797,19 @@
         <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>222</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7969,7 +7827,7 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7986,10 +7844,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8000,7 +7858,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -8012,17 +7870,19 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>391</v>
+        <v>225</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>393</v>
+        <v>228</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -8047,13 +7907,13 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>394</v>
+        <v>79</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -8071,13 +7931,13 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>390</v>
+        <v>230</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
@@ -8086,16 +7946,16 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>397</v>
+        <v>231</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>398</v>
+        <v>232</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -8106,10 +7966,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8117,7 +7977,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>89</v>
@@ -8132,17 +7992,19 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>400</v>
+        <v>212</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>401</v>
+        <v>235</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>403</v>
+        <v>238</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8191,10 +8053,10 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>399</v>
+        <v>239</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>89</v>
@@ -8206,30 +8068,30 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>404</v>
+        <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>405</v>
+        <v>240</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>406</v>
+        <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>407</v>
+        <v>241</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8240,7 +8102,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -8249,21 +8111,21 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
       </c>
@@ -8311,13 +8173,13 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
@@ -8326,13 +8188,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>79</v>
+        <v>405</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>415</v>
+        <v>392</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
@@ -8346,10 +8208,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8360,10 +8222,10 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>79</v>
@@ -8372,18 +8234,18 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>417</v>
+        <v>195</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8407,13 +8269,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8431,13 +8293,13 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
@@ -8449,27 +8311,27 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>79</v>
+        <v>413</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>423</v>
+        <v>79</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>424</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8480,7 +8342,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -8495,13 +8357,13 @@
         <v>195</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8530,10 +8392,10 @@
         <v>199</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8551,13 +8413,13 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
@@ -8566,13 +8428,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>431</v>
+        <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>433</v>
+        <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8586,10 +8448,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8600,7 +8462,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -8612,15 +8474,17 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>212</v>
+        <v>422</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>213</v>
+        <v>423</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8669,25 +8533,25 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>215</v>
+        <v>421</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>216</v>
+        <v>426</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8704,14 +8568,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8730,16 +8594,16 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>136</v>
+        <v>428</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>218</v>
+        <v>429</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>138</v>
+        <v>430</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8765,31 +8629,31 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>79</v>
+        <v>431</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>222</v>
+        <v>427</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8801,13 +8665,13 @@
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>216</v>
+        <v>433</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8824,10 +8688,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8838,7 +8702,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8847,23 +8711,19 @@
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
       </c>
@@ -8911,31 +8771,31 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8946,46 +8806,44 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>275</v>
+        <v>136</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>276</v>
+        <v>218</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
@@ -9021,57 +8879,57 @@
         <v>79</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>438</v>
+        <v>79</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>439</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9085,7 +8943,7 @@
         <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>79</v>
@@ -9094,18 +8952,20 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>441</v>
+        <v>224</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>442</v>
+        <v>225</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>443</v>
+        <v>226</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
       </c>
@@ -9153,7 +9013,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9168,19 +9028,19 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>445</v>
+        <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>432</v>
+        <v>231</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>433</v>
+        <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>79</v>
+        <v>437</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>79</v>
@@ -9188,10 +9048,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9202,7 +9062,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -9214,18 +9074,20 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>447</v>
+        <v>235</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>448</v>
+        <v>236</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
       </c>
@@ -9249,13 +9111,13 @@
         <v>79</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>450</v>
+        <v>79</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -9273,13 +9135,13 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>446</v>
+        <v>239</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
@@ -9291,13 +9153,13 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>452</v>
+        <v>240</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>453</v>
+        <v>241</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9308,10 +9170,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9322,7 +9184,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -9331,21 +9193,21 @@
         <v>79</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>195</v>
+        <v>440</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
       </c>
@@ -9369,13 +9231,13 @@
         <v>79</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>458</v>
+        <v>79</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>459</v>
+        <v>79</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>79</v>
@@ -9393,13 +9255,13 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
@@ -9411,7 +9273,7 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>460</v>
+        <v>433</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
@@ -9428,10 +9290,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9454,17 +9316,15 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>462</v>
+        <v>195</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -9489,13 +9349,13 @@
         <v>79</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>79</v>
+        <v>448</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>79</v>
@@ -9513,7 +9373,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9531,7 +9391,7 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -9548,10 +9408,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9565,7 +9425,7 @@
         <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>79</v>
@@ -9574,17 +9434,15 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>195</v>
+        <v>451</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -9609,13 +9467,13 @@
         <v>79</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>471</v>
+        <v>79</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>472</v>
+        <v>79</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
@@ -9633,7 +9491,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9648,19 +9506,19 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>79</v>
+        <v>454</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>79</v>
+        <v>456</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>79</v>
+        <v>457</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>79</v>
@@ -9668,10 +9526,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9682,7 +9540,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -9694,13 +9552,13 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>212</v>
+        <v>338</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>213</v>
+        <v>459</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>214</v>
+        <v>460</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9751,25 +9609,25 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>215</v>
+        <v>458</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>216</v>
+        <v>461</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9786,21 +9644,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
@@ -9812,17 +9670,15 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>212</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>136</v>
+        <v>213</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9859,31 +9715,31 @@
         <v>79</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
@@ -9906,14 +9762,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9929,23 +9785,21 @@
         <v>79</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>224</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>225</v>
+        <v>136</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
       </c>
@@ -9993,7 +9847,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10005,19 +9859,19 @@
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -10028,42 +9882,46 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>213</v>
+        <v>347</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
       </c>
@@ -10111,25 +9969,25 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>215</v>
+        <v>349</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
@@ -10146,21 +10004,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>79</v>
@@ -10172,17 +10030,15 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>136</v>
+        <v>466</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10207,49 +10063,49 @@
         <v>79</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>79</v>
+        <v>468</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>79</v>
+        <v>469</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>222</v>
+        <v>465</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>216</v>
+        <v>470</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
@@ -10266,10 +10122,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10277,7 +10133,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>89</v>
@@ -10289,23 +10145,19 @@
         <v>79</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>103</v>
+        <v>472</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>235</v>
+        <v>473</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>79</v>
       </c>
@@ -10353,10 +10205,10 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>239</v>
+        <v>471</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>89</v>
@@ -10371,13 +10223,13 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>240</v>
+        <v>475</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>241</v>
+        <v>79</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10388,10 +10240,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10402,7 +10254,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -10411,21 +10263,23 @@
         <v>79</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>212</v>
+        <v>477</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>243</v>
+        <v>478</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>244</v>
+        <v>479</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
       </c>
@@ -10473,13 +10327,13 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>246</v>
+        <v>476</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>79</v>
@@ -10491,13 +10345,13 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>247</v>
+        <v>482</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10508,10 +10362,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10522,30 +10376,30 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>250</v>
+        <v>484</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>79</v>
       </c>
@@ -10569,13 +10423,13 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>79</v>
+        <v>486</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>79</v>
+        <v>487</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -10593,13 +10447,13 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>254</v>
+        <v>483</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>79</v>
@@ -10611,1699 +10465,23 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>255</v>
+        <v>488</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>256</v>
+        <v>79</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>482</v>
+        <v>79</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP85" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP85">
+  <autoFilter ref="A1:AP71">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12313,7 +10491,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -866,33 +866,7 @@
     <t>1287: reference from SURGERY - PATIENT (#130-.01)</t>
   </si>
   <si>
-    <t>Surg.AnesthesiaAgent.PatientIEN
-Surg.AnesthesiaBlockSite.PatientIEN
-Surg.AnesthesiaTechnique.PatientIEN
-Surg.AnesthesiaTestDose.PatientIEN
-Surg.ReferringPhysician.PatientIEN
-Surg.ReplacementFluidType.PatientIEN
-Surg.SurgeryAssistant.PatientIEN
-Surg.SurgeryAssistantOther.PatientIEN
-Surg.SurgeryDelay.PatientIEN
-Surg.SurgeryINTRA.PatientIEN
-Surg.SurgeryIrrigation.PatientIEN
-Surg.SurgeryMedication.PatientIEN
-Surg.SurgeryOccurrenceNonOp.PatientIEN
-Surg.SurgeryOtherProcedure.PatientIEN
-Surg.SurgeryOtherProcedureCPTModifier.PatientIEN
-Surg.SurgeryOtherProcedureDiagnosis.PatientIEN
-Surg.SurgeryPostOpDiagnosis.PatientIEN
-Surg.SurgeryPreOpDiagnosis.PatientIEN
-Surg.SurgeryPrincipalDiagnosis.PatientIEN
-Surg.SurgeryProcedureCPTModifier.PatientIEN
-Surg.SurgeryProcedureOccurrence.PatientIEN
-Surg.SurgeryRequiredBloodProducts.PatientIEN
-Surg.SurgeryReturnCase.PatientIEN
-Surg.SurgORCircSupport.PatientIEN
-Surg.SurgORCircSupportTime.PatientIEN
-Surg.SurgORScrubSupport.PatientIEN
-Surg.SurgORScrubSupportTime.PatientIEN</t>
+    <t>Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReplacementFluidType.PatientIEN,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN</t>
   </si>
   <si>
     <t>Procedure.encounter</t>
@@ -971,42 +945,7 @@
     <t>1286: source value from SURGERY - DATE OF OPERATION (#130-.09)</t>
   </si>
   <si>
-    <t>Surg.AnesthesiaAgent.SurgeryDateTime
-Surg.AnesthesiaBlockSite.SurgeryDateTime
-Surg.AnesthesiaTechnique.SurgeryDateTime
-Surg.AnesthesiaTestDose.SurgeryDateTime
-SPatient.ImplantedProsthesis.SurgeryDateTime
-SPatient.OperationsIndication.SurgeryDateTime
-Surg.ReferringPhysician.SurgeryDateTime
-Surg.ReplacementFluidType.SurgeryDateTime
-Surg.SurgeryAssistant.SurgeryDateTime
-Surg.SurgeryAssistantOther.SurgeryDateTime
-Surg.SurgeryDelay.SurgeryDateTime
-Surg.SurgeryINTRA.SurgeryDateTime
-Surg.SurgeryIrrigation.SurgeryDateTime
-Surg.SurgeryMedication.SurgeryDateTime
-Surg.SurgeryOccurrenceNonOp.SurgeryDateTime
-Surg.SurgeryOtherPostOpDiagnosis.SurgeryDateTime
-Surg.SurgeryOtherProcedure.SurgeryDateTime
-Surg.SurgeryOtherProcedureCPTModifier.SurgeryDateTime
-Surg.SurgeryOtherProcedureDiagnosis.SurgeryDateTime
-Surg.SurgeryPOST.SurgeryDateTime
-Surg.SurgeryPostOpDiagnosis.SurgeryDateTime
-Surg.SurgeryPRE.SurgeryDateTime
-Surg.SurgeryPreOpDiagnosis.SurgeryDateTime
-Surg.SurgeryPrincipalAssociatedDiagnosis.SurgeryDateTime
-Surg.SurgeryPrincipalAssociatedProcedure.SurgeryDateTime
-Surg.SurgeryPrincipalCPTModifier.SurgeryDateTime
-Surg.SurgeryPrincipalDiagnosis.SurgeryDateTime
-Surg.SurgeryProcedureCPTModifier.SurgeryDateTime
-Surg.SurgeryProcedureDiagnosisCode.SurgeryDateTime
-Surg.SurgeryProcedureOccurrence.SurgeryDateTime
-Surg.SurgeryRequiredBloodProducts.SurgeryDateTime
-Surg.SurgeryReturnCase.SurgeryDateTime
-Surg.SurgORCircSupport.SurgeryDateTime
-Surg.SurgORCircSupportTime.SurgeryDateTime
-Surg.SurgORScrubSupport.SurgeryDateTime
-Surg.SurgORScrubSupportTime.SurgeryDateTime</t>
+    <t>Surg.AnesthesiaAgent.SurgeryDateTime,Surg.AnesthesiaBlockSite.SurgeryDateTime,Surg.AnesthesiaTechnique.SurgeryDateTime,Surg.AnesthesiaTestDose.SurgeryDateTime,SPatient.ImplantedProsthesis.SurgeryDateTime,SPatient.OperationsIndication.SurgeryDateTime,Surg.ReferringPhysician.SurgeryDateTime,Surg.ReplacementFluidType.SurgeryDateTime,Surg.SurgeryAssistant.SurgeryDateTime,Surg.SurgeryAssistantOther.SurgeryDateTime,Surg.SurgeryDelay.SurgeryDateTime,Surg.SurgeryINTRA.SurgeryDateTime,Surg.SurgeryIrrigation.SurgeryDateTime,Surg.SurgeryMedication.SurgeryDateTime,Surg.SurgeryOccurrenceNonOp.SurgeryDateTime,Surg.SurgeryOtherPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryOtherProcedure.SurgeryDateTime,Surg.SurgeryOtherProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryOtherProcedureDiagnosis.SurgeryDateTime,Surg.SurgeryPOST.SurgeryDateTime,Surg.SurgeryPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryPRE.SurgeryDateTime,Surg.SurgeryPreOpDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedProcedure.SurgeryDateTime,Surg.SurgeryPrincipalCPTModifier.SurgeryDateTime,Surg.SurgeryPrincipalDiagnosis.SurgeryDateTime,Surg.SurgeryProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryProcedureDiagnosisCode.SurgeryDateTime,Surg.SurgeryProcedureOccurrence.SurgeryDateTime,Surg.SurgeryRequiredBloodProducts.SurgeryDateTime,Surg.SurgeryReturnCase.SurgeryDateTime,Surg.SurgORCircSupport.SurgeryDateTime,Surg.SurgORCircSupportTime.SurgeryDateTime,Surg.SurgORScrubSupport.SurgeryDateTime,Surg.SurgORScrubSupportTime.SurgeryDateTime</t>
   </si>
   <si>
     <t>Procedure.performed[x]:performedPeriod</t>
@@ -1062,8 +1001,7 @@
     <t>1292: source value from SURGERY - TIME OPERATION BEGAN (#130-.22) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
   </si>
   <si>
-    <t>Surg.SurgeryINTRA.BeginOperationDateTime
-Surg.SurgeryPRE.BeginOperationDateTime</t>
+    <t>Surg.SurgeryINTRA.BeginOperationDateTime,Surg.SurgeryPRE.BeginOperationDateTime</t>
   </si>
   <si>
     <t>Procedure.performed[x]:performedPeriod.end</t>
@@ -1096,8 +1034,7 @@
     <t>1293: source value from SURGERY - TIME OPERATION ENDS (#130-.23) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
   </si>
   <si>
-    <t>Surg.SurgeryINTRA.EndOperationDateTime
-Surg.SurgeryPRE.EndOperationDateTime</t>
+    <t>Surg.SurgeryINTRA.EndOperationDateTime,Surg.SurgeryPRE.EndOperationDateTime</t>
   </si>
   <si>
     <t>Procedure.recorder</t>
@@ -1961,7 +1898,7 @@
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="143.515625" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="56.90234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -247,12 +253,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -608,6 +608,9 @@
 </t>
   </si>
   <si>
+    <t>1520: transform using see VistaRulesForProcStat sheet</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -615,9 +618,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1520: transform using see VistaRulesForProcStat sheet</t>
   </si>
   <si>
     <t>Procedure.statusReason</t>
@@ -743,13 +743,13 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
+    <t>1313: fixed value = http://snomed.info/sct#387713003 Surgical procedure</t>
+  </si>
+  <si>
     <t>union(., ./translation)</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>1313: fixed value = http://snomed.info/sct#387713003 Surgical procedure</t>
   </si>
   <si>
     <t>Procedure.category.text</t>
@@ -851,6 +851,12 @@
     <t>The person, animal or group on which the procedure was performed.</t>
   </si>
   <si>
+    <t>1287: reference from SURGERY - PATIENT (#130-.01)</t>
+  </si>
+  <si>
+    <t>Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReplacementFluidType.PatientIEN,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -861,12 +867,6 @@
   </si>
   <si>
     <t>PID-3</t>
-  </si>
-  <si>
-    <t>1287: reference from SURGERY - PATIENT (#130-.01)</t>
-  </si>
-  <si>
-    <t>Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReplacementFluidType.PatientIEN,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN</t>
   </si>
   <si>
     <t>Procedure.encounter</t>
@@ -885,6 +885,9 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
+    <t>1285: reference from SURGERY - VISIT (#130-.015)</t>
+  </si>
+  <si>
     <t>Event.context</t>
   </si>
   <si>
@@ -895,9 +898,6 @@
   </si>
   <si>
     <t>PV1-19</t>
-  </si>
-  <si>
-    <t>1285: reference from SURGERY - VISIT (#130-.015)</t>
   </si>
   <si>
     <t>Procedure.performed[x]</t>
@@ -992,18 +992,18 @@
 </t>
   </si>
   <si>
+    <t>1292: source value from SURGERY - TIME OPERATION BEGAN (#130-.22) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
+  </si>
+  <si>
+    <t>Surg.SurgeryINTRA.BeginOperationDateTime,Surg.SurgeryPRE.BeginOperationDateTime</t>
+  </si>
+  <si>
     <t>./low</t>
   </si>
   <si>
     <t>DR.1</t>
   </si>
   <si>
-    <t>1292: source value from SURGERY - TIME OPERATION BEGAN (#130-.22) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
-  </si>
-  <si>
-    <t>Surg.SurgeryINTRA.BeginOperationDateTime,Surg.SurgeryPRE.BeginOperationDateTime</t>
-  </si>
-  <si>
     <t>Procedure.performed[x]:performedPeriod.end</t>
   </si>
   <si>
@@ -1025,16 +1025,16 @@
     <t>Period.end</t>
   </si>
   <si>
+    <t>1293: source value from SURGERY - TIME OPERATION ENDS (#130-.23) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
+  </si>
+  <si>
+    <t>Surg.SurgeryINTRA.EndOperationDateTime,Surg.SurgeryPRE.EndOperationDateTime</t>
+  </si>
+  <si>
     <t>./high</t>
   </si>
   <si>
     <t>DR.2</t>
-  </si>
-  <si>
-    <t>1293: source value from SURGERY - TIME OPERATION ENDS (#130-.23) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
-  </si>
-  <si>
-    <t>Surg.SurgeryINTRA.EndOperationDateTime,Surg.SurgeryPRE.EndOperationDateTime</t>
   </si>
   <si>
     <t>Procedure.recorder</t>
@@ -1156,6 +1156,12 @@
     <t>A reference to Device supports use cases, such as pacemakers.</t>
   </si>
   <si>
+    <t>1342: reference from SURGERY - FOLEY CATHETER INSERTED BY (#130-.57)</t>
+  </si>
+  <si>
+    <t>Surg.SurgeryINTRA.FoleyCatheterStaffIEN</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1166,12 +1172,6 @@
   </si>
   <si>
     <t>ORC-19/PRT-5</t>
-  </si>
-  <si>
-    <t>1342: reference from SURGERY - FOLEY CATHETER INSERTED BY (#130-.57)</t>
-  </si>
-  <si>
-    <t>Surg.SurgeryINTRA.FoleyCatheterStaffIEN</t>
   </si>
   <si>
     <t>Procedure.performer.onBehalfOf</t>
@@ -1209,16 +1209,16 @@
     <t>Ties a procedure to where the records are likely kept.</t>
   </si>
   <si>
+    <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (#130-.02) case 130-118 NON-OR PROCEDURE == ‘Y’</t>
+  </si>
+  <si>
+    <t>Surg.SurgeryINTRA.OperatingRoomIEN</t>
+  </si>
+  <si>
     <t>.participation[typeCode=LOC].role[classCode=SDLOC]</t>
   </si>
   <si>
     <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (#130-.02) case 130-118 NON-OR PROCEDURE == ‘Y’</t>
-  </si>
-  <si>
-    <t>Surg.SurgeryINTRA.OperatingRoomIEN</t>
   </si>
   <si>
     <t>Procedure.reasonCode</t>
@@ -1433,6 +1433,9 @@
     <t>Any other notes and comments about the procedure.</t>
   </si>
   <si>
+    <t>1288: source value from SURGERY - GENERAL COMMENTS (#130-.28)</t>
+  </si>
+  <si>
     <t>Event.note</t>
   </si>
   <si>
@@ -1440,9 +1443,6 @@
   </si>
   <si>
     <t>NTE</t>
-  </si>
-  <si>
-    <t>1288: source value from SURGERY - GENERAL COMMENTS (#130-.28)</t>
   </si>
   <si>
     <t>Procedure.focalDevice</t>
@@ -1893,12 +1893,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="142.56640625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="143.515625" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="143.515625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="142.56640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="105.16015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2131,16 +2131,16 @@
         <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>79</v>
@@ -2732,13 +2732,13 @@
         <v>79</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>79</v>
@@ -2852,13 +2852,13 @@
         <v>79</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>79</v>
@@ -2972,13 +2972,13 @@
         <v>79</v>
       </c>
       <c r="AL9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>79</v>
@@ -3094,13 +3094,13 @@
         <v>79</v>
       </c>
       <c r="AL10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>79</v>
@@ -3213,22 +3213,22 @@
         <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3331,16 +3331,16 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>79</v>
@@ -3451,16 +3451,16 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3569,16 +3569,16 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3689,16 +3689,16 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3810,13 +3810,13 @@
         <v>189</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>192</v>
@@ -3927,16 +3927,16 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -4048,16 +4048,16 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>79</v>
@@ -4166,13 +4166,13 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4286,13 +4286,13 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4405,10 +4405,10 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4417,10 +4417,10 @@
         <v>232</v>
       </c>
       <c r="AO21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4530,19 +4530,19 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP22" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4647,22 +4647,22 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -4768,13 +4768,13 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4888,13 +4888,13 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -5007,10 +5007,10 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>79</v>
+        <v>257</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -5019,10 +5019,10 @@
         <v>232</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5129,22 +5129,22 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>79</v>
+        <v>259</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5370,19 +5370,19 @@
         <v>277</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -5485,22 +5485,22 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5607,22 +5607,22 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5729,22 +5729,22 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -5850,13 +5850,13 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5970,13 +5970,13 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -6087,19 +6087,19 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>313</v>
+        <v>79</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>314</v>
@@ -6209,19 +6209,19 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>324</v>
+        <v>79</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>325</v>
@@ -6330,16 +6330,16 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6448,16 +6448,16 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -6563,16 +6563,16 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6684,13 +6684,13 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6804,13 +6804,13 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6926,13 +6926,13 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7043,22 +7043,22 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7286,13 +7286,13 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7403,22 +7403,22 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>384</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7523,19 +7523,19 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -7644,13 +7644,13 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7764,13 +7764,13 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7886,7 +7886,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7898,7 +7898,7 @@
         <v>79</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -8005,22 +8005,22 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>79</v>
+        <v>398</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8125,19 +8125,19 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -8248,19 +8248,19 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -8368,13 +8368,13 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8488,13 +8488,13 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8608,13 +8608,13 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8726,13 +8726,13 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8846,13 +8846,13 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8965,10 +8965,10 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>79</v>
+        <v>437</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -8977,10 +8977,10 @@
         <v>232</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>437</v>
+        <v>79</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9090,19 +9090,19 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -9210,13 +9210,13 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9328,13 +9328,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9446,19 +9446,19 @@
         <v>454</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>456</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="64" hidden="true">
@@ -9564,13 +9564,13 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
@@ -9682,13 +9682,13 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9802,13 +9802,13 @@
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -9924,13 +9924,13 @@
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>79</v>
@@ -10042,13 +10042,13 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>79</v>
@@ -10160,13 +10160,13 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10282,13 +10282,13 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10402,13 +10402,13 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file SURGERY (#130) to us-core-procedure</t>
+    <t>This StructureDefinition contains the maps for VistA file SURGERY (130) to us-core-procedure</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -822,13 +822,13 @@
     <t>Procedure.code.coding</t>
   </si>
   <si>
-    <t>1344: source value from SURGERY - PLANNED PRIN PROCEDURE CODE &gt; CPT (#130-27 &gt; 81)</t>
+    <t>1344: source value from SURGERY - PLANNED PRIN PROCEDURE CODE &gt; CPT (130-27 &gt; 81)</t>
   </si>
   <si>
     <t>Procedure.code.text</t>
   </si>
   <si>
-    <t>1343: source value from SURGERY - PRINCIPAL PROCEDURE (#130-26)</t>
+    <t>1343: source value from SURGERY - PRINCIPAL PROCEDURE (130-26)</t>
   </si>
   <si>
     <t>Surg.SurgeryPRE.PrincipalProcedureText</t>
@@ -851,7 +851,7 @@
     <t>The person, animal or group on which the procedure was performed.</t>
   </si>
   <si>
-    <t>1287: reference from SURGERY - PATIENT (#130-.01)</t>
+    <t>1287: reference from SURGERY - PATIENT (130-.01)</t>
   </si>
   <si>
     <t>Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReplacementFluidType.PatientIEN,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN</t>
@@ -885,7 +885,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
-    <t>1285: reference from SURGERY - VISIT (#130-.015)</t>
+    <t>1285: reference from SURGERY - VISIT (130-.015)</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -942,7 +942,7 @@
 </t>
   </si>
   <si>
-    <t>1286: source value from SURGERY - DATE OF OPERATION (#130-.09)</t>
+    <t>1286: source value from SURGERY - DATE OF OPERATION (130-.09)</t>
   </si>
   <si>
     <t>Surg.AnesthesiaAgent.SurgeryDateTime,Surg.AnesthesiaBlockSite.SurgeryDateTime,Surg.AnesthesiaTechnique.SurgeryDateTime,Surg.AnesthesiaTestDose.SurgeryDateTime,SPatient.ImplantedProsthesis.SurgeryDateTime,SPatient.OperationsIndication.SurgeryDateTime,Surg.ReferringPhysician.SurgeryDateTime,Surg.ReplacementFluidType.SurgeryDateTime,Surg.SurgeryAssistant.SurgeryDateTime,Surg.SurgeryAssistantOther.SurgeryDateTime,Surg.SurgeryDelay.SurgeryDateTime,Surg.SurgeryINTRA.SurgeryDateTime,Surg.SurgeryIrrigation.SurgeryDateTime,Surg.SurgeryMedication.SurgeryDateTime,Surg.SurgeryOccurrenceNonOp.SurgeryDateTime,Surg.SurgeryOtherPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryOtherProcedure.SurgeryDateTime,Surg.SurgeryOtherProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryOtherProcedureDiagnosis.SurgeryDateTime,Surg.SurgeryPOST.SurgeryDateTime,Surg.SurgeryPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryPRE.SurgeryDateTime,Surg.SurgeryPreOpDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedProcedure.SurgeryDateTime,Surg.SurgeryPrincipalCPTModifier.SurgeryDateTime,Surg.SurgeryPrincipalDiagnosis.SurgeryDateTime,Surg.SurgeryProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryProcedureDiagnosisCode.SurgeryDateTime,Surg.SurgeryProcedureOccurrence.SurgeryDateTime,Surg.SurgeryRequiredBloodProducts.SurgeryDateTime,Surg.SurgeryReturnCase.SurgeryDateTime,Surg.SurgORCircSupport.SurgeryDateTime,Surg.SurgORCircSupportTime.SurgeryDateTime,Surg.SurgORScrubSupport.SurgeryDateTime,Surg.SurgORScrubSupportTime.SurgeryDateTime</t>
@@ -992,7 +992,7 @@
 </t>
   </si>
   <si>
-    <t>1292: source value from SURGERY - TIME OPERATION BEGAN (#130-.22) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
+    <t>1292: source value from SURGERY - TIME OPERATION BEGAN (130-.22) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.BeginOperationDateTime,Surg.SurgeryPRE.BeginOperationDateTime</t>
@@ -1025,7 +1025,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>1293: source value from SURGERY - TIME OPERATION ENDS (#130-.23) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
+    <t>1293: source value from SURGERY - TIME OPERATION ENDS (130-.23) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.EndOperationDateTime,Surg.SurgeryPRE.EndOperationDateTime</t>
@@ -1156,7 +1156,7 @@
     <t>A reference to Device supports use cases, such as pacemakers.</t>
   </si>
   <si>
-    <t>1342: reference from SURGERY - FOLEY CATHETER INSERTED BY (#130-.57)</t>
+    <t>1342: reference from SURGERY - FOLEY CATHETER INSERTED BY (130-.57)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.FoleyCatheterStaffIEN</t>
@@ -1209,7 +1209,7 @@
     <t>Ties a procedure to where the records are likely kept.</t>
   </si>
   <si>
-    <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (#130-.02) case 130-118 NON-OR PROCEDURE == ‘Y’</t>
+    <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (130-.02) case 130-118 NON-OR PROCEDURE == ‘Y’</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.OperatingRoomIEN</t>
@@ -1260,7 +1260,7 @@
     <t>Procedure.reasonCode.text</t>
   </si>
   <si>
-    <t>1289: source value from SURGERY - PRINCIPAL PRE-OP DIAGNOSIS (#130-32)</t>
+    <t>1289: source value from SURGERY - PRINCIPAL PRE-OP DIAGNOSIS (130-32)</t>
   </si>
   <si>
     <t>Surg.SurgeryPRE.PrincipalPreOpDiagnosisText</t>
@@ -1380,7 +1380,7 @@
     <t>Procedure.complication.coding</t>
   </si>
   <si>
-    <t>1297: fixed value = http://snomed.info/sct#22298006 Myocardial infarction (disorder) when SURGERY - MYOCARDIAL INFARCTION (#130-258) case == ‘Y’</t>
+    <t>1297: fixed value = http://snomed.info/sct#22298006 Myocardial infarction (disorder) when SURGERY - MYOCARDIAL INFARCTION (130-258) case == ‘Y’</t>
   </si>
   <si>
     <t>Procedure.complication.text</t>
@@ -1433,7 +1433,7 @@
     <t>Any other notes and comments about the procedure.</t>
   </si>
   <si>
-    <t>1288: source value from SURGERY - GENERAL COMMENTS (#130-.28)</t>
+    <t>1288: source value from SURGERY - GENERAL COMMENTS (130-.28)</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -1893,7 +1893,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="143.515625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="141.98046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="142.56640625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -854,7 +854,7 @@
     <t>1287: reference from SURGERY - PATIENT (130-.01)</t>
   </si>
   <si>
-    <t>Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReplacementFluidType.PatientIEN,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN</t>
+    <t>SPatient.ImplantedProsthesis.PatientIEN,SPatient.OperationsIndication.PatientIEN,Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReferringPhysician.PatientSID,Surg.ReplacementFluidType.PatientIEN,Surg.ReplacementFluidType.PatientSID,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryIrrigation.PatientSID,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientSID,Surg.SurgeryOtherPostOpDiagnosis.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientSID,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPOST.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientSID,Surg.SurgeryPrincipalAssociatedDiagnosis.PatientIEN,Surg.SurgeryPrincipalAssociatedProcedure.PatientIEN,Surg.SurgeryPrincipalCPTModifier.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureDiagnosisCode.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientSID,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORCircSupportTime.PatientSID,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN,Surg.SurgORScrubSupportTime.PatientSID</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -945,7 +945,7 @@
     <t>1286: source value from SURGERY - DATE OF OPERATION (130-.09)</t>
   </si>
   <si>
-    <t>Surg.AnesthesiaAgent.SurgeryDateTime,Surg.AnesthesiaBlockSite.SurgeryDateTime,Surg.AnesthesiaTechnique.SurgeryDateTime,Surg.AnesthesiaTestDose.SurgeryDateTime,SPatient.ImplantedProsthesis.SurgeryDateTime,SPatient.OperationsIndication.SurgeryDateTime,Surg.ReferringPhysician.SurgeryDateTime,Surg.ReplacementFluidType.SurgeryDateTime,Surg.SurgeryAssistant.SurgeryDateTime,Surg.SurgeryAssistantOther.SurgeryDateTime,Surg.SurgeryDelay.SurgeryDateTime,Surg.SurgeryINTRA.SurgeryDateTime,Surg.SurgeryIrrigation.SurgeryDateTime,Surg.SurgeryMedication.SurgeryDateTime,Surg.SurgeryOccurrenceNonOp.SurgeryDateTime,Surg.SurgeryOtherPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryOtherProcedure.SurgeryDateTime,Surg.SurgeryOtherProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryOtherProcedureDiagnosis.SurgeryDateTime,Surg.SurgeryPOST.SurgeryDateTime,Surg.SurgeryPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryPRE.SurgeryDateTime,Surg.SurgeryPreOpDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedProcedure.SurgeryDateTime,Surg.SurgeryPrincipalCPTModifier.SurgeryDateTime,Surg.SurgeryPrincipalDiagnosis.SurgeryDateTime,Surg.SurgeryProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryProcedureDiagnosisCode.SurgeryDateTime,Surg.SurgeryProcedureOccurrence.SurgeryDateTime,Surg.SurgeryRequiredBloodProducts.SurgeryDateTime,Surg.SurgeryReturnCase.SurgeryDateTime,Surg.SurgORCircSupport.SurgeryDateTime,Surg.SurgORCircSupportTime.SurgeryDateTime,Surg.SurgORScrubSupport.SurgeryDateTime,Surg.SurgORScrubSupportTime.SurgeryDateTime</t>
+    <t>SPatient.ImplantedProsthesis.SurgeryDateTime,SPatient.OperationsIndication.SurgeryDateTime,Surg.AnesthesiaAgent.SurgeryDateTime,Surg.AnesthesiaBlockSite.SurgeryDateTime,Surg.AnesthesiaTechnique.SurgeryDateTime,Surg.AnesthesiaTestDose.SurgeryDateTime,Surg.ReferringPhysician.SurgeryDateTime,Surg.ReplacementFluidType.SurgeryDateTime,Surg.SurgeryAssistant.SurgeryDateTime,Surg.SurgeryAssistantOther.SurgeryDateTime,Surg.SurgeryDelay.SurgeryDateTime,Surg.SurgeryINTRA.SurgeryDateTime,Surg.SurgeryIrrigation.SurgeryDateTime,Surg.SurgeryMedication.SurgeryDateTime,Surg.SurgeryOccurrenceNonOp.SurgeryDateTime,Surg.SurgeryOtherPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryOtherProcedure.SurgeryDateTime,Surg.SurgeryOtherProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryOtherProcedureDiagnosis.SurgeryDateTime,Surg.SurgeryPOST.SurgeryDateTime,Surg.SurgeryPostOpDiagnosis.SurgeryDateTime,Surg.SurgeryPRE.SurgeryDateTime,Surg.SurgeryPreOpDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedDiagnosis.SurgeryDateTime,Surg.SurgeryPrincipalAssociatedProcedure.SurgeryDateTime,Surg.SurgeryPrincipalCPTModifier.SurgeryDateTime,Surg.SurgeryPrincipalDiagnosis.SurgeryDateTime,Surg.SurgeryProcedureCPTModifier.SurgeryDateTime,Surg.SurgeryProcedureDiagnosisCode.SurgeryDateTime,Surg.SurgeryProcedureOccurrence.SurgeryDateTime,Surg.SurgeryRequiredBloodProducts.SurgeryDateTime,Surg.SurgeryReturnCase.SurgeryDateTime,Surg.SurgORCircSupport.SurgeryDateTime,Surg.SurgORCircSupportTime.SurgeryDateTime,Surg.SurgORScrubSupport.SurgeryDateTime,Surg.SurgORScrubSupportTime.SurgeryDateTime</t>
   </si>
   <si>
     <t>Procedure.performed[x]:performedPeriod</t>
@@ -1212,7 +1212,7 @@
     <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (130-.02) case 130-118 NON-OR PROCEDURE == ‘Y’</t>
   </si>
   <si>
-    <t>Surg.SurgeryINTRA.OperatingRoomIEN</t>
+    <t>Surg.SurgeryINTRA.OperatingRoomIEN,Surg.SurgeryPOST.OperatingRoomIEN</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role[classCode=SDLOC]</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -980,7 +980,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1011,7 +1011,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/EncounterOutpatient)
 </t>
   </si>
   <si>
@@ -1956,7 +1956,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>1339-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.34 ANESTHESIOLOGIST SUPVR</t>
+    <t>null-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.34 ANESTHESIOLOGIST SUPVR</t>
   </si>
   <si>
     <t>Procedure.performer:va-10.function.text</t>
@@ -1965,13 +1965,13 @@
     <t>ANESTHESIOLOGIST SUPVR</t>
   </si>
   <si>
-    <t>1339-1: fixed value = ANESTHESIOLOGIST SUPVR</t>
+    <t>null-1: fixed value = ANESTHESIOLOGIST SUPVR</t>
   </si>
   <si>
     <t>Procedure.performer:va-10.actor</t>
   </si>
   <si>
-    <t>1339: reference from SURGERY - ANESTHESIOLOGIST SUPVR (130-.34)</t>
+    <t>null: reference from SURGERY - ANESTHESIOLOGIST SUPVR (130-.34)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.AnesthesiologistSupervisorStaffIEN</t>
@@ -2157,7 +2157,7 @@
     <t>Procedure.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgery.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgery.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8865" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8865" uniqueCount="792">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1391,6 +1391,10 @@
     <t>Procedure.performer:va-0.actor</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
+</t>
+  </si>
+  <si>
     <t>1298: reference from SURGERY - PERFUSIONIST (130-.167)</t>
   </si>
   <si>
@@ -1956,7 +1960,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>null-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.34 ANESTHESIOLOGIST SUPVR</t>
+    <t>1339-2: fixed value = http://va.gov/terminology/vistaDefinedTerms/130#.34 ANESTHESIOLOGIST SUPVR</t>
   </si>
   <si>
     <t>Procedure.performer:va-10.function.text</t>
@@ -1965,13 +1969,13 @@
     <t>ANESTHESIOLOGIST SUPVR</t>
   </si>
   <si>
-    <t>null-1: fixed value = ANESTHESIOLOGIST SUPVR</t>
+    <t>1339-1: fixed value = ANESTHESIOLOGIST SUPVR</t>
   </si>
   <si>
     <t>Procedure.performer:va-10.actor</t>
   </si>
   <si>
-    <t>null: reference from SURGERY - ANESTHESIOLOGIST SUPVR (130-.34)</t>
+    <t>1339: reference from SURGERY - ANESTHESIOLOGIST SUPVR (130-.34)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.AnesthesiologistSupervisorStaffIEN</t>
@@ -2170,7 +2174,7 @@
     <t>Ties a procedure to where the records are likely kept.</t>
   </si>
   <si>
-    <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (130-.02) case 130-118 NON-OR PROCEDURE == ‘Y’</t>
+    <t>1295: reference from SURGERY - OP ROOM PROCEDURE PERFORMED (130-.02) case 130-118 NON-OR PROCEDURE != ‘Y’</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.OperatingRoomIEN,Surg.SurgeryPOST.OperatingRoomIEN</t>
@@ -10215,7 +10219,7 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>408</v>
@@ -10289,10 +10293,10 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>411</v>
@@ -10309,7 +10313,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>415</v>
@@ -10429,13 +10433,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>79</v>
@@ -10549,7 +10553,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>390</v>
@@ -10667,7 +10671,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>391</v>
@@ -10787,7 +10791,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>392</v>
@@ -10909,7 +10913,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>397</v>
@@ -11029,7 +11033,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>428</v>
@@ -11147,7 +11151,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>430</v>
@@ -11267,7 +11271,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>432</v>
@@ -11315,7 +11319,7 @@
         <v>79</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>79</v>
@@ -11369,7 +11373,7 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>79</v>
@@ -11389,7 +11393,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>436</v>
@@ -11437,7 +11441,7 @@
         <v>79</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>79</v>
@@ -11491,7 +11495,7 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>79</v>
@@ -11511,7 +11515,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>406</v>
@@ -11537,7 +11541,7 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>408</v>
@@ -11611,10 +11615,10 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>411</v>
@@ -11631,7 +11635,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>415</v>
@@ -11751,13 +11755,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>79</v>
@@ -11871,7 +11875,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>390</v>
@@ -11989,7 +11993,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>391</v>
@@ -12109,7 +12113,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>392</v>
@@ -12231,7 +12235,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>397</v>
@@ -12351,7 +12355,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>428</v>
@@ -12469,7 +12473,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>430</v>
@@ -12589,7 +12593,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>432</v>
@@ -12637,7 +12641,7 @@
         <v>79</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>79</v>
@@ -12691,7 +12695,7 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>79</v>
@@ -12711,7 +12715,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>436</v>
@@ -12759,7 +12763,7 @@
         <v>79</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>79</v>
@@ -12813,7 +12817,7 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>79</v>
@@ -12833,7 +12837,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>406</v>
@@ -12859,7 +12863,7 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>408</v>
@@ -12933,10 +12937,10 @@
         <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>411</v>
@@ -12953,7 +12957,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>415</v>
@@ -13073,13 +13077,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>79</v>
@@ -13193,7 +13197,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>390</v>
@@ -13311,7 +13315,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>391</v>
@@ -13431,7 +13435,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>392</v>
@@ -13553,7 +13557,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>397</v>
@@ -13673,7 +13677,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>428</v>
@@ -13791,7 +13795,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>430</v>
@@ -13911,7 +13915,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>432</v>
@@ -13959,7 +13963,7 @@
         <v>79</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>79</v>
@@ -14013,7 +14017,7 @@
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>79</v>
@@ -14033,7 +14037,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>436</v>
@@ -14081,7 +14085,7 @@
         <v>79</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>79</v>
@@ -14135,7 +14139,7 @@
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>79</v>
@@ -14155,7 +14159,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>406</v>
@@ -14181,7 +14185,7 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>408</v>
@@ -14255,10 +14259,10 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>411</v>
@@ -14275,7 +14279,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>415</v>
@@ -14395,13 +14399,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>79</v>
@@ -14515,7 +14519,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>390</v>
@@ -14633,7 +14637,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>391</v>
@@ -14753,7 +14757,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>392</v>
@@ -14875,7 +14879,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>397</v>
@@ -14995,7 +14999,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>428</v>
@@ -15113,7 +15117,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>430</v>
@@ -15233,7 +15237,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>432</v>
@@ -15281,7 +15285,7 @@
         <v>79</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>79</v>
@@ -15335,7 +15339,7 @@
         <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>79</v>
@@ -15355,7 +15359,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>436</v>
@@ -15403,7 +15407,7 @@
         <v>79</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>79</v>
@@ -15457,7 +15461,7 @@
         <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>79</v>
@@ -15477,7 +15481,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>406</v>
@@ -15503,7 +15507,7 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>408</v>
@@ -15577,10 +15581,10 @@
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>411</v>
@@ -15597,7 +15601,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>415</v>
@@ -15717,13 +15721,13 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>79</v>
@@ -15837,7 +15841,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>390</v>
@@ -15955,7 +15959,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>391</v>
@@ -16075,7 +16079,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>392</v>
@@ -16197,7 +16201,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>397</v>
@@ -16317,7 +16321,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>428</v>
@@ -16435,7 +16439,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>430</v>
@@ -16555,7 +16559,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>432</v>
@@ -16603,7 +16607,7 @@
         <v>79</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>79</v>
@@ -16657,7 +16661,7 @@
         <v>101</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>79</v>
@@ -16677,7 +16681,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>436</v>
@@ -16725,7 +16729,7 @@
         <v>79</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>79</v>
@@ -16779,7 +16783,7 @@
         <v>101</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>79</v>
@@ -16799,7 +16803,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>406</v>
@@ -16825,7 +16829,7 @@
         <v>90</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L117" t="s" s="2">
         <v>408</v>
@@ -16899,10 +16903,10 @@
         <v>101</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>411</v>
@@ -16919,7 +16923,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>415</v>
@@ -17039,13 +17043,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>79</v>
@@ -17159,7 +17163,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>390</v>
@@ -17277,7 +17281,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>391</v>
@@ -17397,7 +17401,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>392</v>
@@ -17519,7 +17523,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>397</v>
@@ -17639,7 +17643,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>428</v>
@@ -17757,7 +17761,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>430</v>
@@ -17877,7 +17881,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>432</v>
@@ -17925,7 +17929,7 @@
         <v>79</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>79</v>
@@ -17979,7 +17983,7 @@
         <v>101</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>79</v>
@@ -17999,7 +18003,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>436</v>
@@ -18047,7 +18051,7 @@
         <v>79</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>79</v>
@@ -18101,7 +18105,7 @@
         <v>101</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>79</v>
@@ -18121,7 +18125,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>406</v>
@@ -18147,7 +18151,7 @@
         <v>90</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L128" t="s" s="2">
         <v>408</v>
@@ -18221,10 +18225,10 @@
         <v>101</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>411</v>
@@ -18241,7 +18245,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>415</v>
@@ -18361,13 +18365,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>79</v>
@@ -18481,7 +18485,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>390</v>
@@ -18599,7 +18603,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>391</v>
@@ -18719,7 +18723,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>392</v>
@@ -18841,7 +18845,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>397</v>
@@ -18961,7 +18965,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>428</v>
@@ -19079,7 +19083,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>430</v>
@@ -19199,7 +19203,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>432</v>
@@ -19247,7 +19251,7 @@
         <v>79</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>79</v>
@@ -19301,7 +19305,7 @@
         <v>101</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>79</v>
@@ -19321,7 +19325,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>436</v>
@@ -19369,7 +19373,7 @@
         <v>79</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>79</v>
@@ -19423,7 +19427,7 @@
         <v>101</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>79</v>
@@ -19443,7 +19447,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>406</v>
@@ -19469,7 +19473,7 @@
         <v>90</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L139" t="s" s="2">
         <v>408</v>
@@ -19543,10 +19547,10 @@
         <v>101</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>411</v>
@@ -19563,7 +19567,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>415</v>
@@ -19683,13 +19687,13 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>79</v>
@@ -19803,7 +19807,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>390</v>
@@ -19921,7 +19925,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>391</v>
@@ -20041,7 +20045,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>392</v>
@@ -20163,7 +20167,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>397</v>
@@ -20283,7 +20287,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>428</v>
@@ -20401,7 +20405,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>430</v>
@@ -20521,7 +20525,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>432</v>
@@ -20569,7 +20573,7 @@
         <v>79</v>
       </c>
       <c r="S148" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="T148" t="s" s="2">
         <v>79</v>
@@ -20623,7 +20627,7 @@
         <v>101</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>79</v>
@@ -20643,7 +20647,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>436</v>
@@ -20691,7 +20695,7 @@
         <v>79</v>
       </c>
       <c r="S149" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="T149" t="s" s="2">
         <v>79</v>
@@ -20745,7 +20749,7 @@
         <v>101</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>79</v>
@@ -20765,7 +20769,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>406</v>
@@ -20791,7 +20795,7 @@
         <v>90</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L150" t="s" s="2">
         <v>408</v>
@@ -20865,10 +20869,10 @@
         <v>101</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>411</v>
@@ -20885,7 +20889,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>415</v>
@@ -21005,13 +21009,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>79</v>
@@ -21125,7 +21129,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>390</v>
@@ -21243,7 +21247,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>391</v>
@@ -21363,7 +21367,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>392</v>
@@ -21485,7 +21489,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>397</v>
@@ -21605,7 +21609,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>428</v>
@@ -21723,7 +21727,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>430</v>
@@ -21843,7 +21847,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>432</v>
@@ -21891,7 +21895,7 @@
         <v>79</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>79</v>
@@ -21945,7 +21949,7 @@
         <v>101</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>79</v>
@@ -21965,7 +21969,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>436</v>
@@ -22013,7 +22017,7 @@
         <v>79</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>79</v>
@@ -22067,7 +22071,7 @@
         <v>101</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>79</v>
@@ -22087,7 +22091,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>406</v>
@@ -22113,7 +22117,7 @@
         <v>90</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L161" t="s" s="2">
         <v>408</v>
@@ -22187,10 +22191,10 @@
         <v>101</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>411</v>
@@ -22207,7 +22211,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>415</v>
@@ -22327,13 +22331,13 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>79</v>
@@ -22447,7 +22451,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>390</v>
@@ -22565,7 +22569,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>391</v>
@@ -22685,7 +22689,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>392</v>
@@ -22807,7 +22811,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>397</v>
@@ -22927,7 +22931,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>428</v>
@@ -23045,7 +23049,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>430</v>
@@ -23165,7 +23169,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>432</v>
@@ -23213,7 +23217,7 @@
         <v>79</v>
       </c>
       <c r="S170" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="T170" t="s" s="2">
         <v>79</v>
@@ -23267,7 +23271,7 @@
         <v>101</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>79</v>
@@ -23287,7 +23291,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>436</v>
@@ -23335,7 +23339,7 @@
         <v>79</v>
       </c>
       <c r="S171" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="T171" t="s" s="2">
         <v>79</v>
@@ -23389,7 +23393,7 @@
         <v>101</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>79</v>
@@ -23409,7 +23413,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>406</v>
@@ -23435,7 +23439,7 @@
         <v>90</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L172" t="s" s="2">
         <v>408</v>
@@ -23509,10 +23513,10 @@
         <v>101</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>411</v>
@@ -23529,7 +23533,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>415</v>
@@ -23649,13 +23653,13 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>79</v>
@@ -23769,7 +23773,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>390</v>
@@ -23887,7 +23891,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>391</v>
@@ -24007,7 +24011,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>392</v>
@@ -24129,7 +24133,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>397</v>
@@ -24249,7 +24253,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>428</v>
@@ -24367,7 +24371,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>430</v>
@@ -24487,7 +24491,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>432</v>
@@ -24535,7 +24539,7 @@
         <v>79</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>79</v>
@@ -24589,7 +24593,7 @@
         <v>101</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>79</v>
@@ -24609,7 +24613,7 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>436</v>
@@ -24657,7 +24661,7 @@
         <v>79</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>79</v>
@@ -24711,7 +24715,7 @@
         <v>101</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>79</v>
@@ -24731,7 +24735,7 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>406</v>
@@ -24757,7 +24761,7 @@
         <v>90</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L183" t="s" s="2">
         <v>408</v>
@@ -24831,10 +24835,10 @@
         <v>101</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>411</v>
@@ -24851,7 +24855,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>415</v>
@@ -24971,13 +24975,13 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>79</v>
@@ -25091,7 +25095,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>390</v>
@@ -25209,7 +25213,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>391</v>
@@ -25329,7 +25333,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>392</v>
@@ -25451,7 +25455,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>397</v>
@@ -25571,7 +25575,7 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>428</v>
@@ -25689,7 +25693,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>430</v>
@@ -25809,7 +25813,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>432</v>
@@ -25857,7 +25861,7 @@
         <v>79</v>
       </c>
       <c r="S192" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="T192" t="s" s="2">
         <v>79</v>
@@ -25911,7 +25915,7 @@
         <v>101</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AL192" t="s" s="2">
         <v>79</v>
@@ -25931,7 +25935,7 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>436</v>
@@ -25979,7 +25983,7 @@
         <v>79</v>
       </c>
       <c r="S193" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="T193" t="s" s="2">
         <v>79</v>
@@ -26033,7 +26037,7 @@
         <v>101</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AL193" t="s" s="2">
         <v>79</v>
@@ -26053,7 +26057,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>406</v>
@@ -26079,7 +26083,7 @@
         <v>90</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L194" t="s" s="2">
         <v>408</v>
@@ -26153,10 +26157,10 @@
         <v>101</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>411</v>
@@ -26173,7 +26177,7 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>415</v>
@@ -26293,13 +26297,13 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>383</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D196" t="s" s="2">
         <v>79</v>
@@ -26413,7 +26417,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>390</v>
@@ -26531,7 +26535,7 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>391</v>
@@ -26651,7 +26655,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>392</v>
@@ -26773,7 +26777,7 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>397</v>
@@ -26893,7 +26897,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>428</v>
@@ -27011,7 +27015,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>430</v>
@@ -27131,7 +27135,7 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>432</v>
@@ -27179,7 +27183,7 @@
         <v>79</v>
       </c>
       <c r="S203" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="T203" t="s" s="2">
         <v>79</v>
@@ -27233,7 +27237,7 @@
         <v>101</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>79</v>
@@ -27253,7 +27257,7 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>436</v>
@@ -27301,7 +27305,7 @@
         <v>79</v>
       </c>
       <c r="S204" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="T204" t="s" s="2">
         <v>79</v>
@@ -27355,7 +27359,7 @@
         <v>101</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>79</v>
@@ -27375,7 +27379,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>406</v>
@@ -27401,7 +27405,7 @@
         <v>90</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="L205" t="s" s="2">
         <v>408</v>
@@ -27475,10 +27479,10 @@
         <v>101</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AM205" t="s" s="2">
         <v>411</v>
@@ -27495,7 +27499,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>415</v>
@@ -27615,10 +27619,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27641,17 +27645,17 @@
         <v>90</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>79</v>
@@ -27700,7 +27704,7 @@
         <v>79</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -27715,19 +27719,19 @@
         <v>101</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AO207" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AP207" t="s" s="2">
         <v>79</v>
@@ -27735,10 +27739,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27764,13 +27768,13 @@
         <v>195</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -27799,10 +27803,10 @@
         <v>199</v>
       </c>
       <c r="Y208" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Z208" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>79</v>
@@ -27820,7 +27824,7 @@
         <v>79</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -27841,13 +27845,13 @@
         <v>79</v>
       </c>
       <c r="AM208" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AP208" t="s" s="2">
         <v>79</v>
@@ -27855,10 +27859,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27973,10 +27977,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28093,10 +28097,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28215,10 +28219,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28317,10 +28321,10 @@
         <v>101</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AM212" t="s" s="2">
         <v>79</v>
@@ -28337,10 +28341,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28363,16 +28367,16 @@
         <v>90</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -28422,7 +28426,7 @@
         <v>79</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -28443,13 +28447,13 @@
         <v>79</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO213" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AP213" t="s" s="2">
         <v>79</v>
@@ -28457,10 +28461,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28486,13 +28490,13 @@
         <v>195</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
@@ -28521,10 +28525,10 @@
         <v>199</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>79</v>
@@ -28542,7 +28546,7 @@
         <v>79</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -28566,21 +28570,21 @@
         <v>79</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP214" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28606,13 +28610,13 @@
         <v>195</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -28641,10 +28645,10 @@
         <v>199</v>
       </c>
       <c r="Y215" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="Z215" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>79</v>
@@ -28662,7 +28666,7 @@
         <v>79</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -28686,7 +28690,7 @@
         <v>79</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>79</v>
@@ -28697,10 +28701,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28723,16 +28727,16 @@
         <v>79</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -28782,7 +28786,7 @@
         <v>79</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -28806,7 +28810,7 @@
         <v>79</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>79</v>
@@ -28817,10 +28821,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28846,13 +28850,13 @@
         <v>195</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
@@ -28881,10 +28885,10 @@
         <v>199</v>
       </c>
       <c r="Y217" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="Z217" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>79</v>
@@ -28902,7 +28906,7 @@
         <v>79</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
@@ -28926,7 +28930,7 @@
         <v>79</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>79</v>
@@ -28937,10 +28941,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29055,10 +29059,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29175,10 +29179,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29277,7 +29281,7 @@
         <v>101</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>79</v>
@@ -29297,10 +29301,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29399,7 +29403,7 @@
         <v>101</v>
       </c>
       <c r="AK221" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AL221" t="s" s="2">
         <v>79</v>
@@ -29419,10 +29423,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29445,17 +29449,17 @@
         <v>79</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>79</v>
@@ -29504,7 +29508,7 @@
         <v>79</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>80</v>
@@ -29528,7 +29532,7 @@
         <v>79</v>
       </c>
       <c r="AN222" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AO222" t="s" s="2">
         <v>79</v>
@@ -29539,10 +29543,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29568,10 +29572,10 @@
         <v>195</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -29601,10 +29605,10 @@
         <v>199</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>79</v>
@@ -29622,7 +29626,7 @@
         <v>79</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -29646,7 +29650,7 @@
         <v>79</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>79</v>
@@ -29657,10 +29661,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29683,13 +29687,13 @@
         <v>79</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -29740,7 +29744,7 @@
         <v>79</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -29755,30 +29759,30 @@
         <v>101</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AL224" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM224" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP224" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29804,10 +29808,10 @@
         <v>384</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -29858,7 +29862,7 @@
         <v>79</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -29882,7 +29886,7 @@
         <v>79</v>
       </c>
       <c r="AN225" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AO225" t="s" s="2">
         <v>79</v>
@@ -29893,10 +29897,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30011,10 +30015,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30131,10 +30135,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30253,10 +30257,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30282,10 +30286,10 @@
         <v>195</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -30315,10 +30319,10 @@
         <v>113</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>79</v>
@@ -30336,7 +30340,7 @@
         <v>79</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>80</v>
@@ -30360,7 +30364,7 @@
         <v>79</v>
       </c>
       <c r="AN229" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AO229" t="s" s="2">
         <v>79</v>
@@ -30371,10 +30375,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30397,13 +30401,13 @@
         <v>79</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -30454,7 +30458,7 @@
         <v>79</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>89</v>
@@ -30478,7 +30482,7 @@
         <v>79</v>
       </c>
       <c r="AN230" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AO230" t="s" s="2">
         <v>79</v>
@@ -30489,10 +30493,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30515,19 +30519,19 @@
         <v>79</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="O231" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>79</v>
@@ -30576,7 +30580,7 @@
         <v>79</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>80</v>
@@ -30600,7 +30604,7 @@
         <v>79</v>
       </c>
       <c r="AN231" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AO231" t="s" s="2">
         <v>79</v>
@@ -30611,10 +30615,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30640,13 +30644,13 @@
         <v>195</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -30675,10 +30679,10 @@
         <v>199</v>
       </c>
       <c r="Y232" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="Z232" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>79</v>
@@ -30696,7 +30700,7 @@
         <v>79</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>80</v>
@@ -30720,7 +30724,7 @@
         <v>79</v>
       </c>
       <c r="AN232" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AO232" t="s" s="2">
         <v>79</v>
